--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED17.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED17.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>168W</t>
+          <t>127W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-4-0121</t>
+          <t>SIM_XA_FIXED-3-0082</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,11 +1714,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>82W</t>
+          <t>97W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>第4年</t>
+          <t>第3年</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0季</t>
+          <t>3季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G49"/>
+  <dimension ref="B2:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="E14" t="n">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>-14</v>
       </c>
       <c r="E16" t="n">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>-15</v>
       </c>
       <c r="E19" t="n">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="E22" t="n">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
         <v>-14</v>
       </c>
       <c r="E23" t="n">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>-14</v>
       </c>
       <c r="E24" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>-14</v>
       </c>
       <c r="E25" t="n">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2394,14 +2394,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-14</v>
+        <v>-48</v>
       </c>
       <c r="E26" t="n">
-        <v>357</v>
+        <v>315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2420,14 +2420,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-15</v>
+        <v>-32</v>
       </c>
       <c r="E27" t="n">
-        <v>342</v>
+        <v>283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-4ee2df4fe1"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-7866af2c34", "line_id": "L-4ee2df4fe1", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2446,14 +2446,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E28" t="n">
-        <v>342</v>
+        <v>269</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-4ee2df4fe1", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E29" t="n">
-        <v>342</v>
+        <v>254</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-4ee2df4fe1", "asset_type": "production_line"}</t>
+          <t>maintenance_expense | {"line_id": "L-4ee2df4fe1"}</t>
         </is>
       </c>
     </row>
@@ -2498,23 +2498,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>338</v>
+        <v>254</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-4ee2df4fe1", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2524,23 +2524,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>324</v>
+        <v>254</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-4ee2df4fe1", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2550,23 +2550,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-36</v>
+        <v>-8</v>
       </c>
       <c r="E32" t="n">
-        <v>288</v>
+        <v>246</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2576,23 +2576,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-24</v>
+        <v>-14</v>
       </c>
       <c r="E33" t="n">
-        <v>264</v>
+        <v>232</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-fa58de07eb", "line_id": "L-4ee2df4fe1", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2602,14 +2602,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-3-0082", "receivable_term_quarters": 3, "revenue_wan": 97.0}</t>
         </is>
       </c>
     </row>
@@ -2628,23 +2628,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-14</v>
+        <v>-48</v>
       </c>
       <c r="E35" t="n">
-        <v>236</v>
+        <v>184</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2654,23 +2654,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>82</v>
+        <v>-32</v>
       </c>
       <c r="E36" t="n">
-        <v>318</v>
+        <v>152</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 60.0, "order_id": "SIM_XA_FIXED-4-0121", "receivable_term_quarters": 0, "revenue_wan": 82.0}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-fa58de07eb", "line_id": "L-4ee2df4fe1", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2680,23 +2680,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-36</v>
+        <v>-14</v>
       </c>
       <c r="E37" t="n">
-        <v>282</v>
+        <v>138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2706,23 +2706,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-24</v>
+        <v>-14</v>
       </c>
       <c r="E38" t="n">
-        <v>258</v>
+        <v>124</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-d930b07cd6", "line_id": "L-4ee2df4fe1", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2739,7 @@
         <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>244</v>
+        <v>110</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2758,14 +2758,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-15</v>
+        <v>97</v>
       </c>
       <c r="E40" t="n">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-4ee2df4fe1"}</t>
+          <t>receivable_collected | {"receivable_id": "AR-c7ac5b1c93"}</t>
         </is>
       </c>
     </row>
@@ -2784,14 +2784,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E41" t="n">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-4ee2df4fe1", "asset_type": "factory"}</t>
+          <t>maintenance_expense | {"line_id": "L-4ee2df4fe1"}</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-4ee2df4fe1", "asset_type": "production_line"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-4ee2df4fe1", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2836,23 +2836,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-4ee2df4fe1", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2862,14 +2862,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E44" t="n">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2895,11 +2895,11 @@
         <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2921,11 +2921,11 @@
         <v>-14</v>
       </c>
       <c r="E46" t="n">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2940,23 +2940,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E47" t="n">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-4ee2df4fe1"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2966,14 +2966,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E48" t="n">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-4ee2df4fe1", "asset_type": "factory"}</t>
+          <t>maintenance_expense | {"line_id": "L-4ee2df4fe1"}</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3007,6 +3007,32 @@
         </is>
       </c>
       <c r="G49" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-4ee2df4fe1", "asset_type": "factory"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>47</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>127</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-4ee2df4fe1", "asset_type": "production_line"}</t>
         </is>
@@ -3113,16 +3139,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -3338,16 +3364,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G13" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -3406,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3431,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3456,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3475,16 +3501,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F19" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G19" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H19" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -3500,16 +3526,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-75</v>
+        <v>-79</v>
       </c>
       <c r="F20" t="n">
-        <v>-75</v>
+        <v>-79</v>
       </c>
       <c r="G20" t="n">
-        <v>-53</v>
+        <v>-62</v>
       </c>
       <c r="H20" t="n">
-        <v>-61</v>
+        <v>-65</v>
       </c>
     </row>
     <row r="21">
@@ -3550,16 +3576,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-90.2</v>
+        <v>-94.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-90.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-68.2</v>
+        <v>-77.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-76.2</v>
+        <v>-80.2</v>
       </c>
     </row>
     <row r="23">
@@ -3600,16 +3626,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-90.2</v>
+        <v>-94.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-90.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-68.2</v>
+        <v>-77.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-76.2</v>
+        <v>-80.2</v>
       </c>
     </row>
     <row r="25">
@@ -3650,16 +3676,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-90.2</v>
+        <v>-94.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-90.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-68.2</v>
+        <v>-77.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-76.2</v>
+        <v>-80.2</v>
       </c>
     </row>
     <row r="28">
@@ -3749,16 +3775,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F30" t="n">
-        <v>342</v>
+        <v>254</v>
       </c>
       <c r="G30" t="n">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="H30" t="n">
-        <v>168</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31">
@@ -3802,10 +3828,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3830,10 +3856,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H33" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
@@ -3874,16 +3900,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F35" t="n">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="G35" t="n">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="H35" t="n">
-        <v>228</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36">
@@ -3999,16 +4025,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>498.6</v>
+        <v>494.6</v>
       </c>
       <c r="F40" t="n">
-        <v>408.4</v>
+        <v>400.4</v>
       </c>
       <c r="G40" t="n">
-        <v>340.2</v>
+        <v>323.2</v>
       </c>
       <c r="H40" t="n">
-        <v>264</v>
+        <v>243</v>
       </c>
     </row>
     <row r="41">
@@ -4177,13 +4203,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-176.4</v>
+        <v>-180.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-266.6</v>
+        <v>-274.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-334.8</v>
+        <v>-351.8</v>
       </c>
     </row>
     <row r="48">
@@ -4199,16 +4225,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-90.2</v>
+        <v>-94.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-90.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-68.2</v>
+        <v>-77.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-76.2</v>
+        <v>-80.2</v>
       </c>
     </row>
     <row r="49">
@@ -4224,16 +4250,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>498.6</v>
+        <v>494.6</v>
       </c>
       <c r="F49" t="n">
-        <v>408.4</v>
+        <v>400.4</v>
       </c>
       <c r="G49" t="n">
-        <v>340.2</v>
+        <v>323.2</v>
       </c>
       <c r="H49" t="n">
-        <v>264</v>
+        <v>243</v>
       </c>
     </row>
     <row r="50">
@@ -4249,16 +4275,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>498.6</v>
+        <v>494.6</v>
       </c>
       <c r="F50" t="n">
-        <v>408.4</v>
+        <v>400.4</v>
       </c>
       <c r="G50" t="n">
-        <v>340.2</v>
+        <v>323.2</v>
       </c>
       <c r="H50" t="n">
-        <v>264</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -4329,7 +4355,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4478,7 +4504,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4627,7 +4653,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4776,7 +4802,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -4925,7 +4951,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
